--- a/artfynd/S 826-2025 artfynd.xlsx
+++ b/artfynd/S 826-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AZ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132326955</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89325687</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91239069</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107965950</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1224,6 +1249,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89326074</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,6 +1361,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104679230</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1438,6 +1473,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115139116</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1545,6 +1585,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130053674</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1661,6 +1706,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130988849</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1776,6 +1826,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82902924</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1883,6 +1938,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97881123</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1994,6 +2054,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105492286</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2105,6 +2170,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130988850</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2212,6 +2282,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89325725</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2323,6 +2398,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89325830</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2430,6 +2510,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106978068</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2537,6 +2622,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111224643</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2644,6 +2734,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123308973</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2756,6 +2851,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123937266</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2863,6 +2963,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130053924</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2975,6 +3080,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111224644</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3082,6 +3192,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115139051</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3189,6 +3304,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89325693</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3296,6 +3416,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89325723</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3412,6 +3537,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91548314</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3519,6 +3649,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106978069</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3626,6 +3761,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130054028</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3737,6 +3877,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81853825</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3844,6 +3989,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97881238</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3955,6 +4105,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113362334</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4062,6 +4217,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89325722</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4169,6 +4329,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104180351</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4280,6 +4445,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114744597</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4387,6 +4557,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123937292</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4498,6 +4673,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95870170</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4609,6 +4789,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96723341</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4720,6 +4905,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104180352</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4831,6 +5021,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111224037</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4938,6 +5133,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125689582</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5045,6 +5245,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89325682</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5152,6 +5357,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105731446</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5263,6 +5473,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80212420</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5379,6 +5594,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84035282</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5486,6 +5706,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80212422</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5593,6 +5818,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119693348</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5705,6 +5935,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123937291</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5817,6 +6052,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114744594</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5924,6 +6164,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89893261</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6031,6 +6276,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102820346</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6147,8 +6397,65 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111223682</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 826-2025 artfynd.xlsx
+++ b/artfynd/S 826-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ51"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1714,10 +1714,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>82902924</v>
+        <v>135661455</v>
       </c>
       <c r="B11" t="n">
-        <v>57890</v>
+        <v>57977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1725,16 +1725,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100082</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1742,25 +1742,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>376702</v>
+        <v>376784</v>
       </c>
       <c r="R11" t="n">
-        <v>6279699</v>
+        <v>6279702</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1787,22 +1779,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-03-19</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-03-19</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,16 +1820,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82902924</t>
+          <t>https://artportalen.se/Sighting/135661455</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97881123</v>
+        <v>82902924</v>
       </c>
       <c r="B12" t="n">
-        <v>57947</v>
+        <v>57890</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1845,34 +1837,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102977</v>
+        <v>100082</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>376784</v>
+        <v>376702</v>
       </c>
       <c r="R12" t="n">
-        <v>6279522</v>
+        <v>6279699</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,22 +1899,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-11-26</t>
+          <t>2020-03-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-11-26</t>
+          <t>2020-03-19</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,13 +1940,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97881123</t>
+          <t>https://artportalen.se/Sighting/82902924</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105492286</v>
+        <v>97881123</v>
       </c>
       <c r="B13" t="n">
         <v>57947</v>
@@ -1974,21 +1974,17 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>376718</v>
+        <v>376784</v>
       </c>
       <c r="R13" t="n">
-        <v>6279705</v>
+        <v>6279522</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,22 +2011,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-12-11</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-12-11</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,13 +2052,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105492286</t>
+          <t>https://artportalen.se/Sighting/97881123</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130988850</v>
+        <v>105492286</v>
       </c>
       <c r="B14" t="n">
         <v>57947</v>
@@ -2101,10 +2097,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>376707</v>
+        <v>376718</v>
       </c>
       <c r="R14" t="n">
-        <v>6279695</v>
+        <v>6279705</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,22 +2127,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2022-12-11</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2022-12-11</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,16 +2168,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130988850</t>
+          <t>https://artportalen.se/Sighting/105492286</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89325725</v>
+        <v>130988850</v>
       </c>
       <c r="B15" t="n">
-        <v>58327</v>
+        <v>57947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2189,34 +2185,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>102977</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>376796</v>
+        <v>376707</v>
       </c>
       <c r="R15" t="n">
-        <v>6279704</v>
+        <v>6279695</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,22 +2243,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2284,13 +2284,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89325725</t>
+          <t>https://artportalen.se/Sighting/130988850</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89325830</v>
+        <v>89325725</v>
       </c>
       <c r="B16" t="n">
         <v>58327</v>
@@ -2318,21 +2318,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>376827</v>
+        <v>376796</v>
       </c>
       <c r="R16" t="n">
-        <v>6279603</v>
+        <v>6279704</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2359,22 +2355,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,13 +2396,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89325830</t>
+          <t>https://artportalen.se/Sighting/89325725</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106978068</v>
+        <v>89325830</v>
       </c>
       <c r="B17" t="n">
         <v>58327</v>
@@ -2434,17 +2430,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>376626</v>
+        <v>376827</v>
       </c>
       <c r="R17" t="n">
-        <v>6279721</v>
+        <v>6279603</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2471,22 +2471,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,13 +2512,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106978068</t>
+          <t>https://artportalen.se/Sighting/89325830</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111224643</v>
+        <v>106978068</v>
       </c>
       <c r="B18" t="n">
         <v>58327</v>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>376751</v>
+        <v>376626</v>
       </c>
       <c r="R18" t="n">
-        <v>6279699</v>
+        <v>6279721</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2583,22 +2583,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2624,13 +2624,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111224643</t>
+          <t>https://artportalen.se/Sighting/106978068</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123308973</v>
+        <v>111224643</v>
       </c>
       <c r="B19" t="n">
         <v>58327</v>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>376677</v>
+        <v>376751</v>
       </c>
       <c r="R19" t="n">
-        <v>6279706</v>
+        <v>6279699</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2695,22 +2695,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2736,13 +2736,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123308973</t>
+          <t>https://artportalen.se/Sighting/111224643</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123937266</v>
+        <v>123308973</v>
       </c>
       <c r="B20" t="n">
         <v>58327</v>
@@ -2771,21 +2771,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>376583</v>
+        <v>376677</v>
       </c>
       <c r="R20" t="n">
-        <v>6279739</v>
+        <v>6279706</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2812,22 +2807,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2853,13 +2848,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123937266</t>
+          <t>https://artportalen.se/Sighting/123308973</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130053924</v>
+        <v>123937266</v>
       </c>
       <c r="B21" t="n">
         <v>58327</v>
@@ -2888,16 +2883,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>376800</v>
+        <v>376583</v>
       </c>
       <c r="R21" t="n">
-        <v>6279708</v>
+        <v>6279739</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2924,22 +2924,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2965,33 +2965,33 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130053924</t>
+          <t>https://artportalen.se/Sighting/123937266</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111224644</v>
+        <v>130053924</v>
       </c>
       <c r="B22" t="n">
-        <v>58112</v>
+        <v>58327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3000,21 +3000,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>376748</v>
+        <v>376800</v>
       </c>
       <c r="R22" t="n">
-        <v>6279699</v>
+        <v>6279708</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3041,22 +3036,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3082,13 +3077,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111224644</t>
+          <t>https://artportalen.se/Sighting/130053924</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115139051</v>
+        <v>111224644</v>
       </c>
       <c r="B23" t="n">
         <v>58112</v>
@@ -3117,16 +3112,21 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>376644</v>
+        <v>376748</v>
       </c>
       <c r="R23" t="n">
-        <v>6279716</v>
+        <v>6279699</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3153,22 +3153,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3194,16 +3194,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115139051</t>
+          <t>https://artportalen.se/Sighting/111224644</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>89325693</v>
+        <v>115139051</v>
       </c>
       <c r="B24" t="n">
-        <v>58114</v>
+        <v>58112</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,21 +3211,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>376588</v>
+        <v>376644</v>
       </c>
       <c r="R24" t="n">
-        <v>6279731</v>
+        <v>6279716</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3265,22 +3265,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3306,13 +3306,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89325693</t>
+          <t>https://artportalen.se/Sighting/115139051</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>89325723</v>
+        <v>89325693</v>
       </c>
       <c r="B25" t="n">
         <v>58114</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>376795</v>
+        <v>376588</v>
       </c>
       <c r="R25" t="n">
-        <v>6279703</v>
+        <v>6279731</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3377,22 +3377,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3418,13 +3418,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89325723</t>
+          <t>https://artportalen.se/Sighting/89325693</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>91548314</v>
+        <v>89325723</v>
       </c>
       <c r="B26" t="n">
         <v>58114</v>
@@ -3452,26 +3452,17 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>376805</v>
+        <v>376795</v>
       </c>
       <c r="R26" t="n">
-        <v>6279592</v>
+        <v>6279703</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3498,22 +3489,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3539,13 +3530,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91548314</t>
+          <t>https://artportalen.se/Sighting/89325723</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>106978069</v>
+        <v>91548314</v>
       </c>
       <c r="B27" t="n">
         <v>58114</v>
@@ -3573,17 +3564,26 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>376626</v>
+        <v>376805</v>
       </c>
       <c r="R27" t="n">
-        <v>6279721</v>
+        <v>6279592</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3610,22 +3610,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3651,13 +3651,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106978069</t>
+          <t>https://artportalen.se/Sighting/91548314</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130054028</v>
+        <v>106978069</v>
       </c>
       <c r="B28" t="n">
         <v>58114</v>
@@ -3692,10 +3692,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>376757</v>
+        <v>376626</v>
       </c>
       <c r="R28" t="n">
-        <v>6279697</v>
+        <v>6279721</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3722,22 +3722,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3763,55 +3763,51 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130054028</t>
+          <t>https://artportalen.se/Sighting/106978069</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>81853825</v>
+        <v>130054028</v>
       </c>
       <c r="B29" t="n">
-        <v>58636</v>
+        <v>58114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>376831</v>
+        <v>376757</v>
       </c>
       <c r="R29" t="n">
-        <v>6279622</v>
+        <v>6279697</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3838,22 +3834,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2020-01-20</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2020-01-20</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3879,16 +3875,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81853825</t>
+          <t>https://artportalen.se/Sighting/130054028</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>97881238</v>
+        <v>81853825</v>
       </c>
       <c r="B30" t="n">
-        <v>58085</v>
+        <v>58636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,34 +3892,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>205976</v>
+        <v>103044</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>376751</v>
+        <v>376831</v>
       </c>
       <c r="R30" t="n">
-        <v>6279714</v>
+        <v>6279622</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3950,22 +3950,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2021-11-04</t>
+          <t>2020-01-20</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2021-11-04</t>
+          <t>2020-01-20</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3991,33 +3991,33 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97881238</t>
+          <t>https://artportalen.se/Sighting/81853825</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113362334</v>
+        <v>97881238</v>
       </c>
       <c r="B31" t="n">
-        <v>57104</v>
+        <v>58085</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100006</v>
+        <v>205976</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stjärtand</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4025,21 +4025,17 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>376290</v>
+        <v>376751</v>
       </c>
       <c r="R31" t="n">
-        <v>6279654</v>
+        <v>6279714</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4066,22 +4062,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2021-11-04</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2021-11-04</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4107,51 +4103,55 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113362334</t>
+          <t>https://artportalen.se/Sighting/97881238</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>89325722</v>
+        <v>113362334</v>
       </c>
       <c r="B32" t="n">
-        <v>57950</v>
+        <v>57104</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>100006</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>376291</v>
+        <v>376290</v>
       </c>
       <c r="R32" t="n">
-        <v>6279665</v>
+        <v>6279654</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4178,22 +4178,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4219,13 +4219,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89325722</t>
+          <t>https://artportalen.se/Sighting/113362334</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>104180351</v>
+        <v>89325722</v>
       </c>
       <c r="B33" t="n">
         <v>57950</v>
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>376301</v>
+        <v>376291</v>
       </c>
       <c r="R33" t="n">
-        <v>6279661</v>
+        <v>6279665</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4290,22 +4290,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-10-08</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-10-08</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4331,13 +4331,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104180351</t>
+          <t>https://artportalen.se/Sighting/89325722</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>114744597</v>
+        <v>104180351</v>
       </c>
       <c r="B34" t="n">
         <v>57950</v>
@@ -4365,21 +4365,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>376204</v>
+        <v>376301</v>
       </c>
       <c r="R34" t="n">
-        <v>6279559</v>
+        <v>6279661</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4406,22 +4402,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2022-10-08</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2022-10-08</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4447,13 +4443,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114744597</t>
+          <t>https://artportalen.se/Sighting/104180351</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123937292</v>
+        <v>114744597</v>
       </c>
       <c r="B35" t="n">
         <v>57950</v>
@@ -4481,17 +4477,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>376230</v>
+        <v>376204</v>
       </c>
       <c r="R35" t="n">
-        <v>6279576</v>
+        <v>6279559</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4518,22 +4518,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4559,55 +4559,51 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123937292</t>
+          <t>https://artportalen.se/Sighting/114744597</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>95870170</v>
+        <v>123937292</v>
       </c>
       <c r="B36" t="n">
-        <v>57105</v>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102932</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>376285</v>
+        <v>376230</v>
       </c>
       <c r="R36" t="n">
-        <v>6279642</v>
+        <v>6279576</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4634,22 +4630,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4675,13 +4671,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95870170</t>
+          <t>https://artportalen.se/Sighting/123937292</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>96723341</v>
+        <v>95870170</v>
       </c>
       <c r="B37" t="n">
         <v>57105</v>
@@ -4711,7 +4707,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4720,10 +4716,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>376289</v>
+        <v>376285</v>
       </c>
       <c r="R37" t="n">
-        <v>6279657</v>
+        <v>6279642</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4750,22 +4746,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2021-09-02</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2021-09-02</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4791,13 +4787,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96723341</t>
+          <t>https://artportalen.se/Sighting/95870170</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>104180352</v>
+        <v>96723341</v>
       </c>
       <c r="B38" t="n">
         <v>57105</v>
@@ -4827,7 +4823,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4836,10 +4832,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>376305</v>
+        <v>376289</v>
       </c>
       <c r="R38" t="n">
-        <v>6279664</v>
+        <v>6279657</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4866,22 +4862,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2022-10-08</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2022-10-08</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4907,13 +4903,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104180352</t>
+          <t>https://artportalen.se/Sighting/96723341</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>111224037</v>
+        <v>104180352</v>
       </c>
       <c r="B39" t="n">
         <v>57105</v>
@@ -4943,7 +4939,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4952,10 +4948,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>376295</v>
+        <v>376305</v>
       </c>
       <c r="R39" t="n">
-        <v>6279654</v>
+        <v>6279664</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4982,22 +4978,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2022-10-08</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2022-10-08</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5023,13 +5019,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111224037</t>
+          <t>https://artportalen.se/Sighting/104180352</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125689582</v>
+        <v>111224037</v>
       </c>
       <c r="B40" t="n">
         <v>57105</v>
@@ -5057,17 +5053,21 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>376294</v>
+        <v>376295</v>
       </c>
       <c r="R40" t="n">
-        <v>6279656</v>
+        <v>6279654</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5094,22 +5094,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5135,33 +5135,33 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125689582</t>
+          <t>https://artportalen.se/Sighting/111224037</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>89325682</v>
+        <v>125689582</v>
       </c>
       <c r="B41" t="n">
-        <v>57947</v>
+        <v>57105</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102977</v>
+        <v>102932</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>376183</v>
+        <v>376294</v>
       </c>
       <c r="R41" t="n">
-        <v>6279525</v>
+        <v>6279656</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5206,22 +5206,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5247,13 +5247,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89325682</t>
+          <t>https://artportalen.se/Sighting/125689582</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>105731446</v>
+        <v>89325682</v>
       </c>
       <c r="B42" t="n">
         <v>57947</v>
@@ -5288,10 +5288,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>376211</v>
+        <v>376183</v>
       </c>
       <c r="R42" t="n">
-        <v>6279576</v>
+        <v>6279525</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5318,22 +5318,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-01-03</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-01-03</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5359,33 +5359,33 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105731446</t>
+          <t>https://artportalen.se/Sighting/89325682</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>80212420</v>
+        <v>105731446</v>
       </c>
       <c r="B43" t="n">
-        <v>58209</v>
+        <v>57947</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102980</v>
+        <v>102977</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5393,11 +5393,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
@@ -5407,7 +5403,7 @@
         <v>376211</v>
       </c>
       <c r="R43" t="n">
-        <v>6279586</v>
+        <v>6279576</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5434,22 +5430,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2019-09-24</t>
+          <t>2023-01-03</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2019-09-24</t>
+          <t>2023-01-03</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5475,16 +5471,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80212420</t>
+          <t>https://artportalen.se/Sighting/105731446</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>84035282</v>
+        <v>80212420</v>
       </c>
       <c r="B44" t="n">
-        <v>58497</v>
+        <v>58209</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5492,21 +5488,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102990</v>
+        <v>102980</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5514,21 +5510,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>376187</v>
+        <v>376211</v>
       </c>
       <c r="R44" t="n">
-        <v>6279548</v>
+        <v>6279586</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5555,22 +5546,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2019-09-24</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2019-09-24</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5596,33 +5587,33 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84035282</t>
+          <t>https://artportalen.se/Sighting/80212420</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>80212422</v>
+        <v>84035282</v>
       </c>
       <c r="B45" t="n">
-        <v>58327</v>
+        <v>58497</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5630,17 +5621,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>376211</v>
+        <v>376187</v>
       </c>
       <c r="R45" t="n">
-        <v>6279585</v>
+        <v>6279548</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5667,22 +5667,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2019-09-24</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2019-09-24</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5708,13 +5708,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80212422</t>
+          <t>https://artportalen.se/Sighting/84035282</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119693348</v>
+        <v>80212422</v>
       </c>
       <c r="B46" t="n">
         <v>58327</v>
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>376310</v>
+        <v>376211</v>
       </c>
       <c r="R46" t="n">
-        <v>6279666</v>
+        <v>6279585</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5779,22 +5779,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2019-09-24</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2019-09-24</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5820,13 +5820,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119693348</t>
+          <t>https://artportalen.se/Sighting/80212422</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123937291</v>
+        <v>119693348</v>
       </c>
       <c r="B47" t="n">
         <v>58327</v>
@@ -5855,21 +5855,16 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>376184</v>
+        <v>376310</v>
       </c>
       <c r="R47" t="n">
-        <v>6279538</v>
+        <v>6279666</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5896,22 +5891,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5937,33 +5932,33 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123937291</t>
+          <t>https://artportalen.se/Sighting/119693348</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>114744594</v>
+        <v>123937291</v>
       </c>
       <c r="B48" t="n">
-        <v>58112</v>
+        <v>58327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5983,10 +5978,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>376204</v>
+        <v>376184</v>
       </c>
       <c r="R48" t="n">
-        <v>6279561</v>
+        <v>6279538</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6013,22 +6008,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6054,16 +6049,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114744594</t>
+          <t>https://artportalen.se/Sighting/123937291</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>89893261</v>
+        <v>114744594</v>
       </c>
       <c r="B49" t="n">
-        <v>58114</v>
+        <v>58112</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6071,34 +6066,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>376230</v>
+        <v>376204</v>
       </c>
       <c r="R49" t="n">
-        <v>6279599</v>
+        <v>6279561</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6125,22 +6125,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2020-12-06</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2020-12-06</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6166,16 +6166,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89893261</t>
+          <t>https://artportalen.se/Sighting/114744594</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>102820346</v>
+        <v>89893261</v>
       </c>
       <c r="B50" t="n">
-        <v>43219</v>
+        <v>58114</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6183,21 +6183,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>201028</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Thymelicus lineola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ochsenheimer, 1808)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>376308</v>
+        <v>376230</v>
       </c>
       <c r="R50" t="n">
-        <v>6279666</v>
+        <v>6279599</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6237,22 +6237,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2022-07-13</t>
+          <t>2020-12-06</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2022-07-13</t>
+          <t>2020-12-06</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6278,55 +6278,51 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102820346</t>
+          <t>https://artportalen.se/Sighting/89893261</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>111223682</v>
+        <v>102820346</v>
       </c>
       <c r="B51" t="n">
-        <v>56876</v>
+        <v>43219</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>208257</v>
+        <v>201028</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ochsenheimer, 1808)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>376273</v>
+        <v>376308</v>
       </c>
       <c r="R51" t="n">
-        <v>6279643</v>
+        <v>6279666</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6353,27 +6349,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Död</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6398,6 +6389,127 @@
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102820346</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>111223682</v>
+      </c>
+      <c r="B52" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>376273</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6279643</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2023-07-30</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2023-07-30</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Död</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/111223682</t>
         </is>
@@ -6455,6 +6567,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 826-2025 artfynd.xlsx
+++ b/artfynd/S 826-2025 artfynd.xlsx
@@ -1717,7 +1717,7 @@
         <v>135661455</v>
       </c>
       <c r="B11" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 826-2025 artfynd.xlsx
+++ b/artfynd/S 826-2025 artfynd.xlsx
@@ -1717,7 +1717,7 @@
         <v>135661455</v>
       </c>
       <c r="B11" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 826-2025 artfynd.xlsx
+++ b/artfynd/S 826-2025 artfynd.xlsx
@@ -1717,7 +1717,7 @@
         <v>135661455</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 826-2025 artfynd.xlsx
+++ b/artfynd/S 826-2025 artfynd.xlsx
@@ -1717,7 +1717,7 @@
         <v>135661455</v>
       </c>
       <c r="B11" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
